--- a/docs/qms/evidence-2026/16_Lessons_Learnt/EM26-16_Lessons_Learnt_Log.xlsx
+++ b/docs/qms/evidence-2026/16_Lessons_Learnt/EM26-16_Lessons_Learnt_Log.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -851,7 +851,71 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Add API acceptance tests to CI (open).</t>
+          <t>Fixed; 14 regression tests added; API acceptance in CI (open).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>LL-2026-13</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Observability</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>A healthcheck that does not exercise the function it guards stayed green while embeddings failed.</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>NC-2026-016</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Healthcheck to perform a real embedding (open).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>LL-2026-14</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Change control</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Re-testing after a fix found a regression the fix itself introduced (logout logged as anonymous).</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>QA-FAIL-2026-06</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Always re-run the full acceptance suite after a fix (adopted).</t>
         </is>
       </c>
     </row>

--- a/docs/qms/evidence-2026/16_Lessons_Learnt/EM26-16_Lessons_Learnt_Log.xlsx
+++ b/docs/qms/evidence-2026/16_Lessons_Learnt/EM26-16_Lessons_Learnt_Log.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Lessons" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lessons" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/docs/qms/evidence-2026/16_Lessons_Learnt/EM26-16_Lessons_Learnt_Log.xlsx
+++ b/docs/qms/evidence-2026/16_Lessons_Learnt/EM26-16_Lessons_Learnt_Log.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -919,6 +919,102 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>LL-2026-15</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Client reviews</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Off-the-shelf speech-to-speech systems (Kyutai Unmute, NVIDIA PersonaPlex) were either slow or could not use the customer's knowledge base; each client demonstration exposed it early.</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>EM26-18 CR-2026-03/04</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Show working versions to the client early; own dual-loop architecture adopted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>LL-2026-16</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Large documents</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>A 7,300-page regulation (DoD FMR) needs structure-aware retrieval; BookRAG measured worse than section-based retrieval (43/52 vs 50/52).</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>EM26-18 AC-22; 2decb99</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Measure each retrieval method on the golden suite before adopting it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>LL-2026-17</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Deployment</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>A unit taken to a client site may have no network; the hotspot makes it reachable, but its configuration lives only on the device.</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>EM26-18 CR-2026-05, AC-26</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Bring device configuration under version control.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
